--- a/SuppXLS/Scen_PWR_RES_MustRun.xlsx
+++ b/SuppXLS/Scen_PWR_RES_MustRun.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Make variable renewables must-run: NCAP_AF set as FX (instead of default UP) per timeslice, so surplus cannot be curtailed by throttling. Values copied (as values) from Scen_A_SYS_SAD_40TS &gt; PWR_AF. Order this scenario BELOW Scen_A_SYS_SAD_40TS.</t>
+          <t>Make variable renewables must-run from 2025: NCAP_AF set as FX (instead of default UP) per timeslice. 2018-2024 left as normal so historic calibration bounds still apply. Values from Scen_A_SYS_SAD_40TS &gt; PWR_AF. Order BELOW Scen_A_SYS_SAD_40TS.</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J202"/>
+  <dimension ref="B1:J402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Source: Scen_A_SYS_SAD_40TS.xlsx &gt; PWR_AF (2018 values). If you change that file or use the 1TS variant, regenerate this sheet.</t>
+          <t>Source: Scen_A_SYS_SAD_40TS.xlsx &gt; PWR_AF (2018 values). Must-run starts in 2025 so it does not clash with the historic generation bounds for 2018-2024 in Scen_B_SYS_Historic_Bounds &gt; PWR. Year-0 rows (value 5) = carry forward only.</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -6821,6 +6821,6206 @@
       </c>
       <c r="H202" t="n">
         <v>0.452</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>AuNWA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>5</v>
+      </c>
+      <c r="H203" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>AuNWB</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>5</v>
+      </c>
+      <c r="H204" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>AuNWC</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>5</v>
+      </c>
+      <c r="H205" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>AuNWD</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>5</v>
+      </c>
+      <c r="H206" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>AuNWE</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>5</v>
+      </c>
+      <c r="H207" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>AuWDA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>5</v>
+      </c>
+      <c r="H208" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>AuWDB</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>5</v>
+      </c>
+      <c r="H209" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>AuWDC</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>5</v>
+      </c>
+      <c r="H210" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>AuWDD</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>5</v>
+      </c>
+      <c r="H211" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AuWDE</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>5</v>
+      </c>
+      <c r="H212" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SpNWA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>5</v>
+      </c>
+      <c r="H213" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SpNWB</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>5</v>
+      </c>
+      <c r="H214" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SpNWC</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>5</v>
+      </c>
+      <c r="H215" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SpNWD</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>5</v>
+      </c>
+      <c r="H216" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SpNWE</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>5</v>
+      </c>
+      <c r="H217" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SpWDA</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>5</v>
+      </c>
+      <c r="H218" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SpWDB</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>5</v>
+      </c>
+      <c r="H219" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SpWDC</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>5</v>
+      </c>
+      <c r="H220" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SpWDD</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>5</v>
+      </c>
+      <c r="H221" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SpWDE</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>5</v>
+      </c>
+      <c r="H222" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SuNWA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SuNWB</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>5</v>
+      </c>
+      <c r="H224" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SuNWC</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>5</v>
+      </c>
+      <c r="H225" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SuNWD</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>5</v>
+      </c>
+      <c r="H226" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SuNWE</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>5</v>
+      </c>
+      <c r="H227" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SuWDA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>5</v>
+      </c>
+      <c r="H228" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SuWDB</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>5</v>
+      </c>
+      <c r="H229" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SuWDC</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>5</v>
+      </c>
+      <c r="H230" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SuWDD</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>5</v>
+      </c>
+      <c r="H231" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SuWDE</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>5</v>
+      </c>
+      <c r="H232" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>WiNWA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>5</v>
+      </c>
+      <c r="H233" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>WiNWB</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>5</v>
+      </c>
+      <c r="H234" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>WiNWC</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>5</v>
+      </c>
+      <c r="H235" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>WiNWD</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>5</v>
+      </c>
+      <c r="H236" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>WiNWE</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>5</v>
+      </c>
+      <c r="H237" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>WiWDA</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>5</v>
+      </c>
+      <c r="H238" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>WiWDB</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>5</v>
+      </c>
+      <c r="H239" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>WiWDC</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>5</v>
+      </c>
+      <c r="H240" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>WiWDD</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>5</v>
+      </c>
+      <c r="H241" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>WiWDE</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON*</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>5</v>
+      </c>
+      <c r="H242" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>AuNWA</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>5</v>
+      </c>
+      <c r="H243" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>AuNWB</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>5</v>
+      </c>
+      <c r="H244" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>AuNWC</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>5</v>
+      </c>
+      <c r="H245" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>AuNWD</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>5</v>
+      </c>
+      <c r="H246" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>AuNWE</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>5</v>
+      </c>
+      <c r="H247" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>AuWDA</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>5</v>
+      </c>
+      <c r="H248" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>AuWDB</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>5</v>
+      </c>
+      <c r="H249" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>AuWDC</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>5</v>
+      </c>
+      <c r="H250" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>AuWDD</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>5</v>
+      </c>
+      <c r="H251" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>AuWDE</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>5</v>
+      </c>
+      <c r="H252" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>SpNWA</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>5</v>
+      </c>
+      <c r="H253" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>SpNWB</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>5</v>
+      </c>
+      <c r="H254" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SpNWC</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>5</v>
+      </c>
+      <c r="H255" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>SpNWD</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>5</v>
+      </c>
+      <c r="H256" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>SpNWE</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>5</v>
+      </c>
+      <c r="H257" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SpWDA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>5</v>
+      </c>
+      <c r="H258" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SpWDB</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>5</v>
+      </c>
+      <c r="H259" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SpWDC</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>5</v>
+      </c>
+      <c r="H260" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SpWDD</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>5</v>
+      </c>
+      <c r="H261" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SpWDE</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>5</v>
+      </c>
+      <c r="H262" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SuNWA</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>5</v>
+      </c>
+      <c r="H263" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SuNWB</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>5</v>
+      </c>
+      <c r="H264" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>SuNWC</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>5</v>
+      </c>
+      <c r="H265" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SuNWD</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>5</v>
+      </c>
+      <c r="H266" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>SuNWE</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>5</v>
+      </c>
+      <c r="H267" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SuWDA</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>5</v>
+      </c>
+      <c r="H268" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SuWDB</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>5</v>
+      </c>
+      <c r="H269" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SuWDC</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>5</v>
+      </c>
+      <c r="H270" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SuWDD</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>5</v>
+      </c>
+      <c r="H271" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SuWDE</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>5</v>
+      </c>
+      <c r="H272" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>WiNWA</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>5</v>
+      </c>
+      <c r="H273" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>WiNWB</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>5</v>
+      </c>
+      <c r="H274" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>WiNWC</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>5</v>
+      </c>
+      <c r="H275" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>WiNWD</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>5</v>
+      </c>
+      <c r="H276" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>WiNWE</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>5</v>
+      </c>
+      <c r="H277" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>WiWDA</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>5</v>
+      </c>
+      <c r="H278" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>WiWDB</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>5</v>
+      </c>
+      <c r="H279" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>WiWDC</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>5</v>
+      </c>
+      <c r="H280" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>WiWDD</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>5</v>
+      </c>
+      <c r="H281" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>WiWDE</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-OF*</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>5</v>
+      </c>
+      <c r="H282" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>AuNWA</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>5</v>
+      </c>
+      <c r="H283" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>AuNWB</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>5</v>
+      </c>
+      <c r="H284" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>AuNWC</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>5</v>
+      </c>
+      <c r="H285" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>AuNWD</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>5</v>
+      </c>
+      <c r="H286" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>AuNWE</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>5</v>
+      </c>
+      <c r="H287" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>AuWDA</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>5</v>
+      </c>
+      <c r="H288" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>AuWDB</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>5</v>
+      </c>
+      <c r="H289" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>AuWDC</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>5</v>
+      </c>
+      <c r="H290" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>AuWDD</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>5</v>
+      </c>
+      <c r="H291" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>AuWDE</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>5</v>
+      </c>
+      <c r="H292" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SpNWA</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>5</v>
+      </c>
+      <c r="H293" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SpNWB</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>5</v>
+      </c>
+      <c r="H294" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SpNWC</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>5</v>
+      </c>
+      <c r="H295" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SpNWD</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>5</v>
+      </c>
+      <c r="H296" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SpNWE</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>5</v>
+      </c>
+      <c r="H297" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>SpWDA</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>5</v>
+      </c>
+      <c r="H298" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SpWDB</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>5</v>
+      </c>
+      <c r="H299" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SpWDC</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>5</v>
+      </c>
+      <c r="H300" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SpWDD</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>5</v>
+      </c>
+      <c r="H301" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SpWDE</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>5</v>
+      </c>
+      <c r="H302" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>SuNWA</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>5</v>
+      </c>
+      <c r="H303" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>SuNWB</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>5</v>
+      </c>
+      <c r="H304" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>SuNWC</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>5</v>
+      </c>
+      <c r="H305" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>SuNWD</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>5</v>
+      </c>
+      <c r="H306" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SuNWE</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>5</v>
+      </c>
+      <c r="H307" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>SuWDA</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>5</v>
+      </c>
+      <c r="H308" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>SuWDB</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>5</v>
+      </c>
+      <c r="H309" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>SuWDC</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>5</v>
+      </c>
+      <c r="H310" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SuWDD</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>5</v>
+      </c>
+      <c r="H311" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>SuWDE</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>5</v>
+      </c>
+      <c r="H312" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>WiNWA</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>5</v>
+      </c>
+      <c r="H313" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>WiNWB</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>5</v>
+      </c>
+      <c r="H314" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>WiNWC</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>5</v>
+      </c>
+      <c r="H315" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>WiNWD</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>5</v>
+      </c>
+      <c r="H316" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>WiNWE</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>5</v>
+      </c>
+      <c r="H317" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>WiWDA</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>5</v>
+      </c>
+      <c r="H318" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>WiWDB</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>5</v>
+      </c>
+      <c r="H319" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>WiWDC</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>5</v>
+      </c>
+      <c r="H320" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>WiWDD</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>5</v>
+      </c>
+      <c r="H321" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>WiWDE</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>P-RNW-SOL-*</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>5</v>
+      </c>
+      <c r="H322" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>AuNWA</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>5</v>
+      </c>
+      <c r="H323" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>AuNWB</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>5</v>
+      </c>
+      <c r="H324" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>AuNWC</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>0</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>5</v>
+      </c>
+      <c r="H325" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>AuNWD</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>5</v>
+      </c>
+      <c r="H326" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>AuNWE</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>5</v>
+      </c>
+      <c r="H327" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>AuWDA</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>0</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>5</v>
+      </c>
+      <c r="H328" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>AuWDB</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>5</v>
+      </c>
+      <c r="H329" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>AuWDC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>5</v>
+      </c>
+      <c r="H330" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>AuWDD</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>5</v>
+      </c>
+      <c r="H331" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>AuWDE</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>0</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>5</v>
+      </c>
+      <c r="H332" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>SpNWA</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>5</v>
+      </c>
+      <c r="H333" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>SpNWB</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>5</v>
+      </c>
+      <c r="H334" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>SpNWC</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>5</v>
+      </c>
+      <c r="H335" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SpNWD</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>5</v>
+      </c>
+      <c r="H336" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>SpNWE</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>5</v>
+      </c>
+      <c r="H337" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>SpWDA</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>5</v>
+      </c>
+      <c r="H338" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>SpWDB</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>5</v>
+      </c>
+      <c r="H339" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>SpWDC</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>5</v>
+      </c>
+      <c r="H340" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>SpWDD</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>5</v>
+      </c>
+      <c r="H341" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SpWDE</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>5</v>
+      </c>
+      <c r="H342" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SuNWA</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>5</v>
+      </c>
+      <c r="H343" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SuNWB</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>5</v>
+      </c>
+      <c r="H344" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>SuNWC</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>5</v>
+      </c>
+      <c r="H345" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>SuNWD</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>5</v>
+      </c>
+      <c r="H346" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>SuNWE</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>5</v>
+      </c>
+      <c r="H347" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>SuWDA</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>5</v>
+      </c>
+      <c r="H348" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>SuWDB</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>5</v>
+      </c>
+      <c r="H349" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>SuWDC</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>5</v>
+      </c>
+      <c r="H350" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>SuWDD</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>5</v>
+      </c>
+      <c r="H351" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>SuWDE</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>5</v>
+      </c>
+      <c r="H352" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>WiNWA</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>0</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>5</v>
+      </c>
+      <c r="H353" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>WiNWB</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>5</v>
+      </c>
+      <c r="H354" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>WiNWC</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>5</v>
+      </c>
+      <c r="H355" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>WiNWD</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>5</v>
+      </c>
+      <c r="H356" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>WiNWE</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>5</v>
+      </c>
+      <c r="H357" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>WiWDA</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>0</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>5</v>
+      </c>
+      <c r="H358" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>WiWDB</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>5</v>
+      </c>
+      <c r="H359" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>WiWDC</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>5</v>
+      </c>
+      <c r="H360" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>WiWDD</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>5</v>
+      </c>
+      <c r="H361" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>WiWDE</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>P-RNW*WAV*</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>5</v>
+      </c>
+      <c r="H362" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>AuNWA</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>5</v>
+      </c>
+      <c r="H363" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>AuNWB</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>0</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>5</v>
+      </c>
+      <c r="H364" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>AuNWC</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>5</v>
+      </c>
+      <c r="H365" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>AuNWD</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>5</v>
+      </c>
+      <c r="H366" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>AuNWE</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>0</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>5</v>
+      </c>
+      <c r="H367" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>AuWDA</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>0</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>5</v>
+      </c>
+      <c r="H368" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>AuWDB</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>5</v>
+      </c>
+      <c r="H369" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>AuWDC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>0</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>5</v>
+      </c>
+      <c r="H370" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>AuWDD</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>5</v>
+      </c>
+      <c r="H371" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>AuWDE</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>0</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>5</v>
+      </c>
+      <c r="H372" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SpNWA</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>0</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>5</v>
+      </c>
+      <c r="H373" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SpNWB</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>0</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>5</v>
+      </c>
+      <c r="H374" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SpNWC</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>0</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>5</v>
+      </c>
+      <c r="H375" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SpNWD</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>5</v>
+      </c>
+      <c r="H376" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SpNWE</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>5</v>
+      </c>
+      <c r="H377" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SpWDA</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>0</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>5</v>
+      </c>
+      <c r="H378" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SpWDB</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G379" t="n">
+        <v>5</v>
+      </c>
+      <c r="H379" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SpWDC</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>5</v>
+      </c>
+      <c r="H380" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SpWDD</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>5</v>
+      </c>
+      <c r="H381" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SpWDE</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>0</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>5</v>
+      </c>
+      <c r="H382" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SuNWA</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>5</v>
+      </c>
+      <c r="H383" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SuNWB</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>0</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>5</v>
+      </c>
+      <c r="H384" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SuNWC</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>0</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>5</v>
+      </c>
+      <c r="H385" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SuNWD</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>5</v>
+      </c>
+      <c r="H386" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SuNWE</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>5</v>
+      </c>
+      <c r="H387" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SuWDA</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>5</v>
+      </c>
+      <c r="H388" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SuWDB</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>0</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>5</v>
+      </c>
+      <c r="H389" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SuWDC</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>5</v>
+      </c>
+      <c r="H390" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SuWDD</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>5</v>
+      </c>
+      <c r="H391" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SuWDE</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>0</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>5</v>
+      </c>
+      <c r="H392" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>WiNWA</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>5</v>
+      </c>
+      <c r="H393" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>WiNWB</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>5</v>
+      </c>
+      <c r="H394" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>WiNWC</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>0</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>5</v>
+      </c>
+      <c r="H395" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>WiNWD</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>0</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>5</v>
+      </c>
+      <c r="H396" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>WiNWE</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>5</v>
+      </c>
+      <c r="H397" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>WiWDA</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>0</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>5</v>
+      </c>
+      <c r="H398" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>WiWDB</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>0</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>5</v>
+      </c>
+      <c r="H399" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>WiWDC</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>0</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>5</v>
+      </c>
+      <c r="H400" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>WiWDD</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>0</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>5</v>
+      </c>
+      <c r="H401" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>WiWDE</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>0</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>P-RNW*TID*</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>5</v>
+      </c>
+      <c r="H402" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_PWR_RES_MustRun.xlsx
+++ b/SuppXLS/Scen_PWR_RES_MustRun.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PWR_AF_FX" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dump_ban" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13026,4 +13027,119 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>~TFM_INS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>From 2025 curtailed electricity can no longer be dumped: it must all be converted to hydrogen by SH2PCELC_CUR. Year 0 = 5 carries the bound forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>TimeSlice</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>LimType</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Pset_PN</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>P-CURT-DUMP</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P-CURT-DUMP</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SuppXLS/Scen_PWR_RES_MustRun.xlsx
+++ b/SuppXLS/Scen_PWR_RES_MustRun.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PWR_AF_FX" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dump_ban" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AFA_relax" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13142,4 +13143,191 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>~TFM_INS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Why: existing wind (VT_IE_PWR &gt; Processes, AFA = 0.285) and wave/tidal (SubRES_PWR_NewTechs, AFA = 0.36) have an ANNUAL availability cap lower than the average of the forced timeslice profile (offshore 0.497, wave 0.438, tidal 0.447). From 2025 the annual cap is relaxed to 1 so the must-run profile applies; 2024 keeps the original value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>TimeSlice</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>LimType</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Pset_PN</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON00-ROI,P-RNW-WIN-OF00-ROI</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.285</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P-RNW-WIN-ON00-ROI,P-RNW-WIN-OF00-ROI</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P-RNW-OCE-*</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>P-RNW-OCE-*</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SuppXLS/Scen_PWR_RES_MustRun.xlsx
+++ b/SuppXLS/Scen_PWR_RES_MustRun.xlsx
@@ -13204,11 +13204,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ANNUAL</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>UP</t>
@@ -13216,7 +13211,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NCAP_AF</t>
+          <t>NCAP_AFA</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -13235,11 +13230,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ANNUAL</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>UP</t>
@@ -13247,7 +13237,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NCAP_AF</t>
+          <t>NCAP_AFA</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -13266,11 +13256,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ANNUAL</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>UP</t>
@@ -13278,7 +13263,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NCAP_AF</t>
+          <t>NCAP_AFA</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -13297,11 +13282,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ANNUAL</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>UP</t>
@@ -13309,7 +13289,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NCAP_AF</t>
+          <t>NCAP_AFA</t>
         </is>
       </c>
       <c r="E6" t="n">
